--- a/data/trans_camb/P19C04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 7,52</t>
+          <t>-2,2; 7,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 3,01</t>
+          <t>-5,8; 3,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 3,36</t>
+          <t>-8,48; 3,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,07</t>
+          <t>1,51; 9,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,89</t>
+          <t>-2,99; 4,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 0,11</t>
+          <t>-7,29; 0,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,04</t>
+          <t>0,97; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,33</t>
+          <t>-3,35; 2,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,66</t>
+          <t>-6,34; 0,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 85,18</t>
+          <t>-15,25; 90,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 36,07</t>
+          <t>-44,15; 39,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,93; 38,47</t>
+          <t>-69,03; 39,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 176,24</t>
+          <t>15,28; 163,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 86,02</t>
+          <t>-33,28; 77,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,09; 8,19</t>
+          <t>-79,1; 3,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 89,01</t>
+          <t>9,2; 94,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 29,56</t>
+          <t>-31,71; 32,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 15,74</t>
+          <t>-62,99; 11,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 9,01</t>
+          <t>0,34; 9,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,74</t>
+          <t>-4,16; 4,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 2,28</t>
+          <t>-7,41; 2,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,78</t>
+          <t>-2,85; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,18</t>
+          <t>-2,9; 5,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 0,71</t>
+          <t>-8,03; 0,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,78</t>
+          <t>-0,27; 5,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,68</t>
+          <t>-2,26; 3,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; -0,27</t>
+          <t>-6,72; -0,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 78,08</t>
+          <t>1,8; 78,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 40,77</t>
+          <t>-25,76; 41,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 19,25</t>
+          <t>-47,41; 23,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 52,89</t>
+          <t>-22,1; 53,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 59,95</t>
+          <t>-22,39; 57,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,94; 7,62</t>
+          <t>-63,01; 3,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 53,41</t>
+          <t>-2,46; 50,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 33,79</t>
+          <t>-15,57; 35,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -1,81</t>
+          <t>-49,83; -2,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,03</t>
+          <t>-0,14; 9,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,32</t>
+          <t>-8,99; -0,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -2,34</t>
+          <t>-11,4; -2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 5,22</t>
+          <t>-2,76; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 1,51</t>
+          <t>-6,29; 1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,65</t>
+          <t>-7,9; -0,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,89</t>
+          <t>-0,19; 5,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,04</t>
+          <t>-6,23; -0,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; -2,68</t>
+          <t>-8,15; -2,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 56,31</t>
+          <t>-1,36; 57,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 3,15</t>
+          <t>-42,29; -0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -13,47</t>
+          <t>-53,97; -13,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 46,11</t>
+          <t>-18,21; 45,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 14,5</t>
+          <t>-41,15; 9,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,28; -6,61</t>
+          <t>-52,41; -5,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 41,89</t>
+          <t>-1,01; 42,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -0,22</t>
+          <t>-37,09; -1,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,78; -19,25</t>
+          <t>-48,34; -18,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,37</t>
+          <t>-8,77; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -3,79</t>
+          <t>-14,78; -3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -11,25</t>
+          <t>-25,13; -11,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 3,25</t>
+          <t>-7,04; 3,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -2,92</t>
+          <t>-13,01; -3,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -7,13</t>
+          <t>-15,26; -6,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,1</t>
+          <t>-6,0; 1,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -4,72</t>
+          <t>-12,03; -5,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -10,43</t>
+          <t>-18,72; -10,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 13,91</t>
+          <t>-29,31; 16,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,72; -14,92</t>
+          <t>-48,6; -14,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-84,38; -43,57</t>
+          <t>-83,99; -43,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 19,2</t>
+          <t>-31,02; 22,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -17,26</t>
+          <t>-56,28; -17,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -40,86</t>
+          <t>-65,76; -40,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 10,18</t>
+          <t>-23,38; 6,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,24; -21,66</t>
+          <t>-47,49; -23,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,82; -47,62</t>
+          <t>-75,32; -46,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 12,71</t>
+          <t>-1,7; 12,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,99</t>
+          <t>-6,85; 7,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,55; -0,41</t>
+          <t>-13,02; -0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,26</t>
+          <t>-4,49; 8,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -1,79</t>
+          <t>-13,12; -1,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,61; -1,59</t>
+          <t>-11,39; -1,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 8,95</t>
+          <t>-0,77; 8,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 0,86</t>
+          <t>-8,13; 1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,46; -2,35</t>
+          <t>-10,38; -2,52</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 57,02</t>
+          <t>-6,8; 56,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,24; 30,67</t>
+          <t>-22,23; 31,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,0; -1,46</t>
+          <t>-41,82; -2,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 50,06</t>
+          <t>-19,52; 51,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,84; -9,49</t>
+          <t>-55,87; -7,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -10,26</t>
+          <t>-46,98; -8,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 43,4</t>
+          <t>-3,23; 43,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 4,13</t>
+          <t>-32,04; 4,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,37; -11,78</t>
+          <t>-39,62; -11,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 18,14</t>
+          <t>-0,04; 17,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 6,01</t>
+          <t>-11,06; 6,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 0,88</t>
+          <t>-12,7; 1,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 10,43</t>
+          <t>-2,73; 11,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 4,5</t>
+          <t>-8,78; 4,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -2,04</t>
+          <t>-20,43; -2,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 11,53</t>
+          <t>1,22; 12,47</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 3,17</t>
+          <t>-8,1; 2,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,88; -2,99</t>
+          <t>-18,51; -3,38</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 72,69</t>
+          <t>-0,07; 70,43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 23,93</t>
+          <t>-34,03; 25,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 3,18</t>
+          <t>-37,3; 6,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 63,66</t>
+          <t>-12,21; 68,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 27,39</t>
+          <t>-38,43; 27,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,39; -12,02</t>
+          <t>-81,5; -13,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,33; 52,69</t>
+          <t>4,18; 57,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 15,02</t>
+          <t>-29,81; 12,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-67,39; -13,22</t>
+          <t>-68,31; -15,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,05; 26,79</t>
+          <t>4,26; 26,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 13,15</t>
+          <t>-6,58; 13,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 8,25</t>
+          <t>-8,53; 8,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,07; 17,33</t>
+          <t>2,21; 17,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 17,26</t>
+          <t>0,56; 17,43</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 8,1</t>
+          <t>-4,05; 8,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,8; 18,12</t>
+          <t>5,25; 18,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 13,17</t>
+          <t>-0,63; 12,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 6,92</t>
+          <t>-3,35; 7,07</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16,11; 141,19</t>
+          <t>12,17; 134,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 71,58</t>
+          <t>-22,27; 69,94</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 43,31</t>
+          <t>-27,32; 44,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,8; 139,88</t>
+          <t>9,98; 140,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,0; 132,4</t>
+          <t>1,63; 139,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 66,73</t>
+          <t>-18,02; 69,16</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,46; 108,68</t>
+          <t>22,39; 111,01</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 80,27</t>
+          <t>-3,08; 80,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 43,01</t>
+          <t>-13,92; 44,44</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,2</t>
+          <t>2,52; 7,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,14</t>
+          <t>-4,17; 0,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,18</t>
+          <t>-8,61; -3,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,68</t>
+          <t>0,98; 4,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,16</t>
+          <t>-3,55; 0,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,6; -2,49</t>
+          <t>-6,57; -2,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,38</t>
+          <t>2,21; 5,3</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,37</t>
+          <t>-3,19; -0,34</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -3,18</t>
+          <t>-6,47; -3,15</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,62; 38,29</t>
+          <t>12,37; 37,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 0,77</t>
+          <t>-20,25; 0,53</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-43,77; -16,69</t>
+          <t>-43,49; -17,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,15; 34,4</t>
+          <t>6,27; 35,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 1,08</t>
+          <t>-23,02; 1,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-42,44; -18,24</t>
+          <t>-42,41; -18,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,99; 32,41</t>
+          <t>12,21; 32,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -2,27</t>
+          <t>-17,79; -2,1</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-37,57; -19,33</t>
+          <t>-36,86; -19,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C04-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C04-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-2,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-3,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,63</t>
+          <t>-2,29; 7,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,01</t>
+          <t>-6,09; 2,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,41</t>
+          <t>-7,95; 3,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,97</t>
+          <t>1,23; 9,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,57</t>
+          <t>-3,06; 4,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,12</t>
+          <t>-6,91; 1,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,43</t>
+          <t>1,02; 7,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,68</t>
+          <t>-3,61; 2,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,58</t>
+          <t>-6,48; 0,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-31,64%</t>
+          <t>-26,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-49,12%</t>
+          <t>-43,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-36,41%</t>
+          <t>-32,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 90,58</t>
+          <t>-19,84; 80,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 39,06</t>
+          <t>-47,52; 31,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,03; 39,85</t>
+          <t>-63,5; 40,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 163,0</t>
+          <t>9,31; 156,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 77,54</t>
+          <t>-32,44; 79,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,1; 3,62</t>
+          <t>-72,65; 20,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 94,28</t>
+          <t>8,9; 96,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 32,95</t>
+          <t>-33,24; 34,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,99; 11,93</t>
+          <t>-61,26; 10,58</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>-2,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 9,29</t>
+          <t>0,18; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 4,85</t>
+          <t>-4,11; 4,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,6</t>
+          <t>-6,77; 3,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,78</t>
+          <t>-2,74; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 5,18</t>
+          <t>-2,62; 4,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 0,36</t>
+          <t>-5,44; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,73</t>
+          <t>-0,2; 5,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,78</t>
+          <t>-2,2; 3,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,72; -0,28</t>
+          <t>-5,14; 1,25</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,69%</t>
+          <t>-15,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-31,38%</t>
+          <t>-16,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-27,18%</t>
+          <t>-16,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 78,04</t>
+          <t>0,44; 75,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 41,36</t>
+          <t>-25,28; 37,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 23,44</t>
+          <t>-44,07; 23,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 53,82</t>
+          <t>-21,29; 53,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 57,35</t>
+          <t>-21,76; 53,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 3,16</t>
+          <t>-45,3; 20,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 50,74</t>
+          <t>-1,57; 54,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 35,58</t>
+          <t>-15,19; 33,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,83; -2,46</t>
+          <t>-36,51; 11,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,9</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,31</t>
+          <t>-4,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 9,38</t>
+          <t>-0,52; 9,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -0,05</t>
+          <t>-8,88; -0,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -2,06</t>
+          <t>-9,25; -0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,11</t>
+          <t>-2,73; 5,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,05</t>
+          <t>-6,05; 1,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -0,78</t>
+          <t>-7,33; -0,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,95</t>
+          <t>-0,08; 6,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,14</t>
+          <t>-5,86; -0,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -2,56</t>
+          <t>-6,91; -1,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-37,34%</t>
+          <t>-25,76%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,64%</t>
+          <t>-30,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-34,42%</t>
+          <t>-26,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 57,31</t>
+          <t>-2,71; 56,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,29; -0,0</t>
+          <t>-42,82; -1,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -13,25</t>
+          <t>-45,17; -3,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 45,68</t>
+          <t>-17,77; 46,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 9,9</t>
+          <t>-40,06; 13,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,41; -5,71</t>
+          <t>-48,56; -3,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 42,98</t>
+          <t>-0,28; 44,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,09; -1,19</t>
+          <t>-34,64; -1,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,34; -18,21</t>
+          <t>-40,69; -9,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-17,22</t>
+          <t>-12,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-10,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,8</t>
+          <t>-11,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 3,81</t>
+          <t>-8,7; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -3,57</t>
+          <t>-15,38; -3,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,13; -11,43</t>
+          <t>-17,39; -7,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 3,96</t>
+          <t>-6,96; 3,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -3,1</t>
+          <t>-13,19; -3,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,26; -6,74</t>
+          <t>-14,59; -6,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,57</t>
+          <t>-5,87; 1,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -5,18</t>
+          <t>-12,4; -5,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -10,03</t>
+          <t>-14,5; -7,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-62,51%</t>
+          <t>-44,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,09%</t>
+          <t>-51,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-58,45%</t>
+          <t>-47,74%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,31; 16,21</t>
+          <t>-28,67; 11,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,6; -14,62</t>
+          <t>-49,53; -11,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,99; -43,38</t>
+          <t>-56,95; -29,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 22,47</t>
+          <t>-30,41; 18,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -17,8</t>
+          <t>-57,62; -21,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,76; -40,46</t>
+          <t>-63,09; -38,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 6,89</t>
+          <t>-23,23; 7,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,49; -23,5</t>
+          <t>-48,21; -22,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-75,32; -46,66</t>
+          <t>-55,66; -36,23</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,47</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,35</t>
+          <t>-6,42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,14</t>
+          <t>-5,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 12,86</t>
+          <t>-1,48; 12,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 7,05</t>
+          <t>-5,88; 7,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,02; -0,7</t>
+          <t>-11,82; -0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 8,64</t>
+          <t>-4,08; 8,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -1,28</t>
+          <t>-12,98; -1,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,39; -1,37</t>
+          <t>-11,77; -1,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,95</t>
+          <t>-0,78; 8,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 1,06</t>
+          <t>-8,08; 1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -2,52</t>
+          <t>-9,94; -1,75</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-24,61%</t>
+          <t>-21,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,36%</t>
+          <t>-31,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-26,65%</t>
+          <t>-25,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 56,26</t>
+          <t>-5,51; 56,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 31,03</t>
+          <t>-19,59; 35,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -2,31</t>
+          <t>-38,96; 0,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 51,2</t>
+          <t>-17,73; 49,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -7,1</t>
+          <t>-54,61; -8,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,98; -8,51</t>
+          <t>-47,29; -10,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 43,99</t>
+          <t>-3,56; 42,69</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 4,89</t>
+          <t>-31,4; 7,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -11,77</t>
+          <t>-37,8; -8,07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-6,09</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-9,39</t>
+          <t>-4,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,99</t>
+          <t>-5,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 17,69</t>
+          <t>-0,05; 18,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 6,34</t>
+          <t>-11,51; 5,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 1,34</t>
+          <t>-14,17; 0,18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 11,42</t>
+          <t>-3,45; 10,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 4,4</t>
+          <t>-8,47; 5,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -2,59</t>
+          <t>-9,86; 0,65</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,47</t>
+          <t>1,02; 12,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 2,81</t>
+          <t>-8,05; 2,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-18,51; -3,38</t>
+          <t>-9,68; -0,78</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,68%</t>
+          <t>-22,48%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-47,1%</t>
+          <t>-20,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-36,95%</t>
+          <t>-21,21%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 70,43</t>
+          <t>-0,45; 72,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 25,43</t>
+          <t>-33,53; 23,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 6,4</t>
+          <t>-39,56; 0,81</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 68,83</t>
+          <t>-14,47; 63,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-38,43; 27,31</t>
+          <t>-36,97; 34,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,5; -13,62</t>
+          <t>-40,26; 4,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,18; 57,92</t>
+          <t>3,9; 59,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 12,89</t>
+          <t>-30,25; 11,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -15,13</t>
+          <t>-34,86; -3,82</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,26; 26,49</t>
+          <t>4,26; 26,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 13,71</t>
+          <t>-6,62; 13,38</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 8,25</t>
+          <t>-9,31; 8,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,21; 17,44</t>
+          <t>2,11; 17,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,56; 17,43</t>
+          <t>0,22; 17,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,36</t>
+          <t>-4,85; 7,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,25; 18,09</t>
+          <t>6,42; 18,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 12,73</t>
+          <t>-0,37; 13,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 7,07</t>
+          <t>-3,38; 6,5</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,17; 134,08</t>
+          <t>12,88; 146,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 69,94</t>
+          <t>-23,25; 69,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 44,84</t>
+          <t>-29,23; 49,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9,98; 140,1</t>
+          <t>9,99; 145,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,63; 139,65</t>
+          <t>0,89; 133,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 69,16</t>
+          <t>-21,87; 58,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,39; 111,01</t>
+          <t>26,58; 111,26</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 80,0</t>
+          <t>-2,08; 79,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 44,44</t>
+          <t>-14,37; 40,79</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>-3,32</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,13</t>
+          <t>2,46; 7,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,13</t>
+          <t>-4,02; 0,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -3,2</t>
+          <t>-5,81; -1,6</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,74</t>
+          <t>1,04; 4,88</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,22</t>
+          <t>-3,51; 0,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -2,5</t>
+          <t>-4,9; -1,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,3</t>
+          <t>2,27; 5,27</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,34</t>
+          <t>-3,51; -0,44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -3,15</t>
+          <t>-4,56; -2,07</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-17,95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-28,39%</t>
+          <t>-21,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-27,64%</t>
+          <t>-19,31%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>12,37; 37,62</t>
+          <t>11,63; 37,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 0,53</t>
+          <t>-19,34; 1,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-43,49; -17,26</t>
+          <t>-27,19; -8,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,27; 35,02</t>
+          <t>6,6; 35,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 1,65</t>
+          <t>-22,41; 1,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-42,41; -18,18</t>
+          <t>-30,54; -12,32</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,21; 32,94</t>
+          <t>12,47; 31,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -2,1</t>
+          <t>-19,17; -2,6</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -19,06</t>
+          <t>-25,4; -12,53</t>
         </is>
       </c>
     </row>
